--- a/data/trans_dic/P19C11_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19C11_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por implantes / solo 2023</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por implantes / solo 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,1</t>
+          <t>0,0; 3,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,98</t>
+          <t>0,05; 1,95</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,3</t>
+          <t>1,2; 5,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,29</t>
+          <t>0,54; 3,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,49</t>
+          <t>1,19; 3,52</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,41</t>
+          <t>2,08; 5,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,08</t>
+          <t>1,26; 3,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,0</t>
+          <t>1,89; 3,84</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 6,13</t>
+          <t>1,36; 5,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,25; 6,82</t>
+          <t>4,3; 7,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 5,8</t>
+          <t>2,76; 6,02</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,01; 7,73</t>
+          <t>3,88; 7,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,49; 8,8</t>
+          <t>5,57; 8,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,16; 7,52</t>
+          <t>5,11; 7,51</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,38; 11,32</t>
+          <t>6,56; 11,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,23; 6,18</t>
+          <t>1,25; 6,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,87; 7,56</t>
+          <t>2,72; 7,62</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,63</t>
+          <t>4,23; 8,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,42</t>
+          <t>3,47; 6,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,15; 6,74</t>
+          <t>4,21; 6,72</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,32; 5,03</t>
+          <t>3,15; 4,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,49</t>
+          <t>3,14; 4,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,41; 4,54</t>
+          <t>3,46; 4,53</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por implantes / solo 2023</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por implantes / solo 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6252</t>
+          <t>0; 6365</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 12460</t>
+          <t>0; 10849</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>168; 13614</t>
+          <t>322; 13397</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4830; 21329</t>
+          <t>4829; 20634</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3016; 16419</t>
+          <t>2694; 16876</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10582; 31517</t>
+          <t>10729; 31732</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10942; 28364</t>
+          <t>10908; 28542</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6654; 16405</t>
+          <t>6718; 16822</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20174; 42269</t>
+          <t>19915; 40556</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13941; 52899</t>
+          <t>11776; 50187</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29778; 47788</t>
+          <t>30101; 49926</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40602; 90699</t>
+          <t>43094; 94100</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>21921; 42243</t>
+          <t>21212; 41825</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>29361; 47047</t>
+          <t>29752; 46174</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55758; 81324</t>
+          <t>55296; 81216</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>22933; 40686</t>
+          <t>23570; 40438</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7394; 37058</t>
+          <t>7495; 36538</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27496; 72511</t>
+          <t>26135; 73082</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11232; 23774</t>
+          <t>11668; 24608</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14081; 26233</t>
+          <t>14194; 26864</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28411; 46096</t>
+          <t>28783; 45988</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>111338; 168678</t>
+          <t>105752; 163532</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>113688; 160699</t>
+          <t>112396; 161142</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>236545; 314939</t>
+          <t>239540; 314375</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C11_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19C11_2023-Edad-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,57</t>
+          <t>0,0; 3,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,95</t>
+          <t>0,17; 2,43</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,13</t>
+          <t>1,64; 6,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,38</t>
+          <t>0,67; 3,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,52</t>
+          <t>1,47; 4,08</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,45</t>
+          <t>1,98; 5,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,16</t>
+          <t>1,35; 3,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,84</t>
+          <t>1,91; 3,82</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,82</t>
+          <t>3,46; 6,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,3; 7,13</t>
+          <t>4,58; 7,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,02</t>
+          <t>4,43; 6,59</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,88; 7,65</t>
+          <t>3,94; 7,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,57; 8,64</t>
+          <t>5,4; 8,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,11; 7,51</t>
+          <t>4,97; 7,3</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,56; 11,25</t>
+          <t>6,37; 11,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,25; 6,09</t>
+          <t>4,26; 7,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,72; 7,62</t>
+          <t>5,68; 8,55</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,23; 8,93</t>
+          <t>4,01; 8,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,57</t>
+          <t>3,16; 6,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,21; 6,72</t>
+          <t>4,21; 6,83</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,15; 4,88</t>
+          <t>3,94; 5,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,5</t>
+          <t>3,71; 4,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,46; 4,53</t>
+          <t>3,98; 4,86</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>5177</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6365</t>
+          <t>0; 5616</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 10849</t>
+          <t>0; 13492</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>322; 13397</t>
+          <t>1221; 17567</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10614</t>
+          <t>14834</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>8065</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18789</t>
+          <t>22899</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4829; 20634</t>
+          <t>7292; 27854</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2694; 16876</t>
+          <t>3240; 16323</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10729; 31732</t>
+          <t>13617; 37887</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>19783</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>13209</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29021</t>
+          <t>32992</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10908; 28542</t>
+          <t>11897; 30623</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6718; 16822</t>
+          <t>8193; 20315</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19915; 40556</t>
+          <t>23032; 46128</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>32181</t>
+          <t>34115</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>38348</t>
+          <t>41919</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70529</t>
+          <t>76034</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11776; 50187</t>
+          <t>23476; 46015</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30101; 49926</t>
+          <t>33042; 52230</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43094; 94100</t>
+          <t>62058; 92304</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>30277</t>
+          <t>32392</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>36767</t>
+          <t>40163</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67045</t>
+          <t>72555</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>21212; 41825</t>
+          <t>23354; 43778</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>29752; 46174</t>
+          <t>32184; 50136</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55296; 81216</t>
+          <t>59058; 86797</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>31053</t>
+          <t>33635</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>24409</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53444</t>
+          <t>58044</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>23570; 40438</t>
+          <t>25339; 44473</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7495; 36538</t>
+          <t>18266; 32130</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26135; 73082</t>
+          <t>46927; 70658</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>17209</t>
+          <t>19305</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>19662</t>
+          <t>20399</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>39704</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11668; 24608</t>
+          <t>12116; 27193</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14194; 26864</t>
+          <t>14082; 27507</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28783; 45988</t>
+          <t>31532; 51120</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>140674</t>
+          <t>155262</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>138912</t>
+          <t>152143</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>279587</t>
+          <t>307405</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>105752; 163532</t>
+          <t>133792; 180390</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>112396; 161142</t>
+          <t>134476; 173205</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>239540; 314375</t>
+          <t>279706; 341573</t>
         </is>
       </c>
     </row>
